--- a/AAII_Financials/Quarterly/PNGAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PNGAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="92">
   <si>
     <t>PNGAY</t>
   </si>
@@ -656,74 +656,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -769,8 +772,11 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,8 +822,11 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +872,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -882,8 +894,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -929,8 +942,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -976,8 +992,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1023,8 +1042,11 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1070,8 +1092,11 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1086,8 +1111,9 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1133,8 +1159,11 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1180,8 +1209,11 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1199,8 +1231,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1246,8 +1279,11 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1293,8 +1329,11 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1340,8 +1379,11 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1387,8 +1429,11 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1434,8 +1479,11 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1481,8 +1529,11 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1528,8 +1579,11 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1575,8 +1629,11 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1622,8 +1679,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1669,8 +1729,11 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1716,8 +1779,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1763,8 +1829,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1810,8 +1879,11 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1857,8 +1929,11 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1904,8 +1979,11 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1951,60 +2029,66 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2022,8 +2106,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2041,149 +2126,159 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>86735100</v>
+        <v>58460900</v>
       </c>
       <c r="E41" s="3">
+        <v>105215200</v>
+      </c>
+      <c r="F41" s="3">
         <v>63867800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>131415900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>58449000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>68184500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>52311800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>70059200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13598100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>75355200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>44723500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>61486600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>33887700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>76658600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>51359700</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>430067900</v>
+      </c>
+      <c r="E42" s="3">
         <v>434411200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>416054600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>392062200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>366694500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>334657500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>341761500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>331818800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>314068700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>290191700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>279904800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>259118100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>259967600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>262842000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>252845500</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>44007900</v>
+        <v>98137700</v>
       </c>
       <c r="E43" s="3">
+        <v>6632900</v>
+      </c>
+      <c r="F43" s="3">
         <v>86899500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6304800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>80781000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>160290100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>70185500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>145102900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>119728100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>109592800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>61104000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>116397200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>134210000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>110892700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>61002300</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2229,243 +2324,261 @@
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>36939400</v>
+        <v>13898100</v>
       </c>
       <c r="E45" s="3">
+        <v>12933700</v>
+      </c>
+      <c r="F45" s="3">
         <v>15384300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13090400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9650300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10050600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13526500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9673400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>16985000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9714000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10625700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12569000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>19709200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6366000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17352500</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>604335100</v>
+        <v>630286300</v>
       </c>
       <c r="E46" s="3">
+        <v>561434500</v>
+      </c>
+      <c r="F46" s="3">
         <v>610343800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>544980300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>543641100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>575296100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>507830600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>558800500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>495279400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>486910700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>430518300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>451590700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>496037100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>458876600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>419506000</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>902970500</v>
+      </c>
+      <c r="E47" s="3">
         <v>824404400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>831620300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>779626400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>802173600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>693607400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>746151400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>668180900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>706834600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>625985600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>674705200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>592580000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>628721600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>621761800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>648173500</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7909100</v>
+      </c>
+      <c r="E48" s="3">
         <v>7661100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7900000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7347200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7657800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7625900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7827000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8362100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7712000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7999600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8489000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8382100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8051500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9303800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9603500</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3213800</v>
+        <v>12028300</v>
       </c>
       <c r="E49" s="3">
+        <v>8739500</v>
+      </c>
+      <c r="F49" s="3">
         <v>11935000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8522200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13826900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13715000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13325300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13916000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10372400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13586300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13972600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13498600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10637900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14403300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>14413200</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2511,8 +2624,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2558,55 +2674,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>24737100</v>
+      </c>
+      <c r="E52" s="3">
         <v>92213200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>22799500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>77543100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>24335400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>36438600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>20042500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>36545300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>31946600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>41251900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>25047600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>34915900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>21676200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>39632700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>23768200</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2652,55 +2774,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2105310600</v>
+      </c>
+      <c r="E54" s="3">
         <v>2054389600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1987085500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1917349300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1885809100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1816734500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1775263700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1786832400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1682514700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1659482900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1633560900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1571386500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1581233100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1643203700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1596291200</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2718,8 +2846,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2737,290 +2866,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>39397300</v>
+      </c>
+      <c r="E57" s="3">
         <v>905300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>904700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>986100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1072300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>974600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1019300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1150000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>29968500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1070700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1256700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1248900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>28510100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1510800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1515700</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>87912300</v>
+      </c>
+      <c r="E58" s="3">
         <v>110963100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>106661000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>108284900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>86113900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>69313600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>80644600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>41261200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>51188000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>33705800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>49660600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>29257900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>56835600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>41398900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>59810800</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>543944200</v>
+      </c>
+      <c r="E59" s="3">
         <v>11136700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>175046900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10211800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>177244800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9771500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>166308300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7655700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>169386100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7879000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>168850800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10587900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>180446500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6808100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>171848400</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>708982700</v>
+      </c>
+      <c r="E60" s="3">
         <v>164453400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>326282900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>155304000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>290030300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>80059700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>281886300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>50067000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>272607600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>42655500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>245909100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>41094800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>290437100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>49717700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>261443600</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>167937100</v>
+      </c>
+      <c r="E61" s="3">
         <v>181289300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>176103000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>165629300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>159725100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>247801600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>161645000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>259828600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>160414100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>273534500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>185292400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>248405600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>176791900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>260858000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>185406100</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1013443400</v>
+      </c>
+      <c r="E62" s="3">
         <v>1499774600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1280259200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1402462600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1247337600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1303056700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1150071800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1292502700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1073461400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1169279600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1026045800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1111062100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>941034300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1150969400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>974224900</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3066,8 +3214,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3113,8 +3264,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3160,55 +3314,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1891248700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1846443200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1784639600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1724426200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1698324800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1632193800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1596514000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1604411600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1508444600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1487453200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1460245200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1402528700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1410289400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1463666100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1424338000</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3226,8 +3386,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3273,8 +3434,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3320,8 +3484,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3367,8 +3534,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3414,55 +3584,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>147296300</v>
+      </c>
+      <c r="E72" s="3">
         <v>139878100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>134405000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>131784000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>124360000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>99501100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>116490400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>99577900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>111772100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>91221700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>107823700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>87150300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>105487600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>91821300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>104856300</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3508,8 +3684,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3555,8 +3734,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3602,55 +3784,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>151349100</v>
+      </c>
+      <c r="E76" s="3">
         <v>147636800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>143031400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>138555700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>131766900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>129502200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>127221200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>129437500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>128143800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>125333400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>126783800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>123770400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>126600500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>133106000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>126020800</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3696,60 +3884,66 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3795,8 +3989,11 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3814,55 +4011,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E83" s="3">
+      <c r="D83" s="3">
+        <v>963000</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3">
         <v>2092200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-1228000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1009100</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3">
         <v>2438600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>-1200600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1041900</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3">
         <v>2484300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>-1202200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1124100</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R83" s="3">
         <v>2338900</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3908,8 +4109,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3955,8 +4159,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4002,8 +4209,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4049,8 +4259,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4096,55 +4309,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>34885900</v>
+      </c>
+      <c r="E89" s="3">
         <v>19001900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>45534300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>275600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13256100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>33517700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4814700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>16071600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>31640000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10381300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6734700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>20605600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-6575700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>30569200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>20012900</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4162,55 +4381,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-242300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-201800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-505800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-290300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-188000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-193300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-494300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-181900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-147200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-337500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-347600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-202300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-205800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-483700</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4256,8 +4479,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4303,55 +4529,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>16066100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-17823200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-16171100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-35295100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7043900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-19997500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-28745500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8259700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-20410400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-24500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9686800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>351300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1420400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4014300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>5531200</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4369,55 +4601,59 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2814500</v>
+      </c>
+      <c r="E96" s="3">
         <v>627200</v>
       </c>
-      <c r="E96" s="3">
-        <v>685800</v>
-      </c>
       <c r="F96" s="3">
-        <v>2509100</v>
+        <v>1613100</v>
       </c>
       <c r="G96" s="3">
-        <v>4360700</v>
+        <v>1598100</v>
       </c>
       <c r="H96" s="3">
+        <v>4105900</v>
+      </c>
+      <c r="I96" s="3">
         <v>548200</v>
       </c>
-      <c r="I96" s="3">
-        <v>1009000</v>
-      </c>
       <c r="J96" s="3">
+        <v>2316300</v>
+      </c>
+      <c r="K96" s="3">
         <v>5804500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>958200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>258000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>2490200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>419600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>3857700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>292600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>2568700</v>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4463,8 +4699,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4510,8 +4749,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4557,145 +4799,157 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-46472300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8526500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7881400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>34951100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5016500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-11351600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>31458500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6220400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-19680100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1665000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>7792000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-23730000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-699100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-14425300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-16598900</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E101" s="3">
+      <c r="D101" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3">
         <v>404800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-348000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>120600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-351200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-60600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>799200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-136800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>72300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>633800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>687100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-162600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-181700</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4211400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7535700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>21071700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-62600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1187200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2168500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1696800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1243400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8448400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8812400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4488700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2833600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7896000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>11992800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>9017600</v>
       </c>
     </row>
